--- a/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-hla-genotype.xlsx
+++ b/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-hla-genotype.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$51</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="452">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T19:29:11+00:00</t>
+    <t>2026-09-03T14:51:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A profile for HLA genotype observations. Each instance represents a genotype for a single HLA locus, expressed as a GL String Code.</t>
+    <t>A profile for HLA genotype observations. Each instance represents a genotype for a single HLA locus, expressed as a GL String Code. The Observation.code uses a locus-specific LOINC code identifying which HLA gene was typed.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -585,6 +585,9 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
+    <t>final</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -634,31 +637,10 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory</t>
-  </si>
-  <si>
-    <t>laboratory</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-    &lt;code value="laboratory"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -668,10 +650,10 @@
 </t>
   </si>
   <si>
-    <t>Genotype display name (LOINC 84413-4)</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
+    <t>HLA locus-specific LOINC code (e.g., 57290-9 for HLA-A)</t>
+  </si>
+  <si>
+    <t>A LOINC code identifying the specific HLA locus typed. Each locus has its own code (HLA-A: 57290-9, HLA-B: 57291-7, HLA-C: 57297-4, HLA-DRB1: 57293-3, HLA-DQB1: 57299-0, HLA-DPB1: 59017-4, HLA-DQA1: 59019-0, HLA-DPA1: 59018-2, HLA-DRB3: 57294-1, HLA-DRB4: 57295-8, HLA-DRB5: 57296-6).</t>
   </si>
   <si>
     <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
@@ -680,22 +662,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="84413-4"/&gt;
-    &lt;display value="Genotype display name"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+    <t>http://fhir.nmdp.org/ig/donor-patient/ValueSet/nmdp-hla-locus-loinc-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -723,7 +690,7 @@
 </t>
   </si>
   <si>
-    <t>The donor whose HLA was typed</t>
+    <t>The donor or CBU whose HLA was typed</t>
   </si>
   <si>
     <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
@@ -812,7 +779,7 @@
 PeriodTiminginstant</t>
   </si>
   <si>
-    <t>When the typing was performed</t>
+    <t>Clinically relevant time/time-period for observation</t>
   </si>
   <si>
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
@@ -1028,6 +995,9 @@
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1381,10 +1351,6 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:code}
-</t>
-  </si>
-  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -1410,6 +1376,12 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1458,54 +1430,6 @@
   </si>
   <si>
     <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
-  </si>
-  <si>
-    <t>Observation.component:geneStudied</t>
-  </si>
-  <si>
-    <t>geneStudied</t>
-  </si>
-  <si>
-    <t>Observation.component:geneStudied.id</t>
-  </si>
-  <si>
-    <t>Observation.component:geneStudied.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:geneStudied.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:geneStudied.code</t>
-  </si>
-  <si>
-    <t>Gene studied (LOINC 48018-6)</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="48018-6"/&gt;
-    &lt;display value="Gene studied [ID]"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Observation.component:geneStudied.value[x]</t>
-  </si>
-  <si>
-    <t>HLA gene name (HGNC ID)</t>
-  </si>
-  <si>
-    <t>http://fhir.nmdp.org/ig/donor-patient/ValueSet/nmdp-hla-gene-name-vs</t>
-  </si>
-  <si>
-    <t>Observation.component:geneStudied.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Observation.component:geneStudied.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component:geneStudied.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -1822,10 +1746,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP61"/>
+  <dimension ref="A1:AP51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.6328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1850,7 +1774,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.0859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.4765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -3486,7 +3410,7 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>82</v>
@@ -3501,13 +3425,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3540,19 +3464,19 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3560,10 +3484,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3571,13 +3495,13 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>82</v>
@@ -3586,19 +3510,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3626,26 +3550,28 @@
         <v>117</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3669,27 +3595,25 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AP15" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
-      <c r="A16" t="s" s="2">
+      <c r="B16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3699,28 +3623,28 @@
         <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3730,7 +3654,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3745,13 +3669,11 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3769,13 +3691,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -3784,34 +3706,34 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3830,19 +3752,19 @@
         <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3852,7 +3774,7 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>82</v>
@@ -3867,34 +3789,34 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="Z17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>205</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>93</v>
@@ -3906,30 +3828,30 @@
         <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>220</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3937,13 +3859,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>82</v>
@@ -3952,20 +3874,18 @@
         <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -4013,13 +3933,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -4028,19 +3948,19 @@
         <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>227</v>
+        <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>229</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4048,21 +3968,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
@@ -4085,7 +4005,9 @@
       <c r="N19" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="O19" s="2"/>
+      <c r="O19" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4133,13 +4055,13 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
@@ -4148,19 +4070,19 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4168,14 +4090,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4194,19 +4116,19 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4255,7 +4177,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4270,34 +4192,34 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4307,7 +4229,7 @@
         <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>82</v>
@@ -4316,20 +4238,18 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4377,7 +4297,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4392,19 +4312,19 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4412,10 +4332,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4426,7 +4346,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4438,18 +4358,18 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N22" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="O22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4497,13 +4417,13 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4512,19 +4432,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4532,10 +4452,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4543,10 +4463,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>94</v>
@@ -4558,17 +4478,19 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>268</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="O23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4593,13 +4515,11 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4617,45 +4537,45 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4663,34 +4583,34 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4715,11 +4635,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4737,7 +4659,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4746,7 +4668,7 @@
         <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>105</v>
@@ -4755,38 +4677,38 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>284</v>
+        <v>136</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4798,19 +4720,19 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4835,13 +4757,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4859,16 +4781,16 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>105</v>
@@ -4877,31 +4799,31 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>136</v>
+        <v>299</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4920,19 +4842,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>191</v>
+        <v>303</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4957,13 +4879,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4981,7 +4903,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4999,27 +4921,27 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5030,7 +4952,7 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5042,7 +4964,7 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>310</v>
+        <v>192</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>311</v>
@@ -5053,9 +4975,7 @@
       <c r="N27" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="O27" t="s" s="2">
-        <v>314</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5079,13 +4999,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5103,13 +5023,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5121,27 +5041,27 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5164,18 +5084,20 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5199,31 +5121,31 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>212</v>
+        <v>314</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5241,27 +5163,27 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5284,20 +5206,18 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>331</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5321,13 +5241,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5345,7 +5265,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5363,27 +5283,27 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5397,7 +5317,7 @@
         <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
@@ -5406,16 +5326,16 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5465,7 +5385,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5483,27 +5403,27 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5514,7 +5434,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5526,18 +5446,20 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5585,45 +5507,45 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>354</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5634,7 +5556,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5646,20 +5568,16 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5707,19 +5625,19 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -5728,7 +5646,7 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>362</v>
@@ -5749,14 +5667,14 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5768,15 +5686,17 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N33" s="2"/>
+      <c r="N33" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5825,19 +5745,19 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5849,7 +5769,7 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5860,14 +5780,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>138</v>
+        <v>367</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5880,24 +5800,26 @@
         <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>140</v>
+        <v>368</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5945,7 +5867,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5969,7 +5891,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>368</v>
+        <v>136</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5980,46 +5902,42 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>139</v>
+        <v>372</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6067,31 +5985,31 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AG35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AN35" t="s" s="2">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6102,10 +6020,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6128,7 +6046,7 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>379</v>
@@ -6185,7 +6103,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6194,7 +6112,7 @@
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>105</v>
@@ -6206,10 +6124,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6220,10 +6138,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6246,16 +6164,20 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>378</v>
+        <v>192</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6279,13 +6201,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6303,7 +6225,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6312,7 +6234,7 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6321,13 +6243,13 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>387</v>
+        <v>300</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6338,10 +6260,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6352,7 +6274,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6364,19 +6286,19 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6401,13 +6323,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>117</v>
+        <v>314</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6425,13 +6347,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6443,13 +6365,13 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6460,10 +6382,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6474,7 +6396,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6486,19 +6408,17 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>399</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6523,13 +6443,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6547,13 +6467,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6565,13 +6485,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>307</v>
+        <v>403</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6608,18 +6528,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>408</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6688,10 +6606,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6702,10 +6620,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6716,7 +6634,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6725,18 +6643,20 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>364</v>
+        <v>409</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6785,13 +6705,13 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
@@ -6806,10 +6726,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>382</v>
+        <v>413</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6820,10 +6740,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6846,16 +6766,16 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6905,7 +6825,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6926,7 +6846,7 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>420</v>
@@ -6966,18 +6886,20 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7046,10 +6968,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7060,10 +6982,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7071,11 +6993,11 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G44" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7083,23 +7005,19 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7135,29 +7053,31 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>361</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7166,10 +7086,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>434</v>
+        <v>362</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7180,21 +7100,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7206,15 +7126,17 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N45" s="2"/>
+      <c r="N45" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7263,19 +7185,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7287,7 +7209,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7298,14 +7220,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>138</v>
+        <v>367</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7318,24 +7240,26 @@
         <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>140</v>
+        <v>368</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7383,7 +7307,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7407,7 +7331,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>368</v>
+        <v>136</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7418,45 +7342,45 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>374</v>
+        <v>432</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>375</v>
+        <v>433</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>142</v>
+        <v>434</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7481,13 +7405,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7505,34 +7429,34 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>431</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>136</v>
+        <v>211</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7551,7 +7475,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -7566,19 +7490,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>439</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>210</v>
+        <v>273</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7603,13 +7527,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7630,7 +7554,7 @@
         <v>438</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>93</v>
@@ -7645,27 +7569,27 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>217</v>
+        <v>277</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>218</v>
+        <v>278</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7685,10 +7609,10 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>444</v>
+        <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>445</v>
@@ -7700,7 +7624,7 @@
         <v>447</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7725,13 +7649,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7749,7 +7673,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7758,7 +7682,7 @@
         <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -7767,38 +7691,38 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>284</v>
+        <v>136</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7810,19 +7734,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>450</v>
+        <v>292</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>451</v>
+        <v>293</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>452</v>
+        <v>294</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7847,13 +7771,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7871,16 +7795,16 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -7889,31 +7813,31 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>136</v>
+        <v>299</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7932,19 +7856,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>191</v>
+        <v>83</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>299</v>
+        <v>450</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>300</v>
+        <v>451</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>301</v>
+        <v>352</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7969,13 +7893,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -7993,7 +7917,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8011,1237 +7935,23 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="D53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y58" s="2"/>
-      <c r="Z58" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP61" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP61">
+  <autoFilter ref="A1:AP51">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9251,7 +7961,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI50">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-hla-genotype.xlsx
+++ b/publication/web-root/matchsync-donor/0.1.0/StructureDefinition-nmdp-hla-genotype.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:51:12+00:00</t>
+    <t>2026-09-03T16:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
